--- a/docs/막지스톡_할인율산식_검증.xlsx
+++ b/docs/막지스톡_할인율산식_검증.xlsx
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D10" s="31" t="inlineStr">
         <is>
-          <t>거의 무상관 — 서로 다른 정보를 담고 있어 합산이 정당</t>
+          <t>절댓값이 0에 가까움 — 더해도 같은 것을 두 번 세지 않음. 부호는 91일 표본에서 p=0.042로 경계선이라 근거로 쓰지 않음</t>
         </is>
       </c>
     </row>
